--- a/NBFC-MF/Borrowers/Thongam_Bala_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Bala_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>2800</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2717.9798966815056</v>
+        <v>1372.4796393105025</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>17282.020103318493</v>
+        <v>18627.520360689497</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1290,31 +1290,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="str">
+      <c r="A17" s="19">
+        <v>46206</v>
+      </c>
+      <c r="B17" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>54.499742628996877</v>
+      </c>
+      <c r="F17" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
+        <v>1345.500257371003</v>
+      </c>
+      <c r="G17" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1372.4796393105025</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>18627.520360689497</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>

--- a/NBFC-MF/Borrowers/Thongam_Bala_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Bala_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>1372.4796393105025</v>
+        <v>9.1336005425546318E-10</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>18627.520360689497</v>
+        <v>19999.999999999087</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1327,31 +1327,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22" t="str">
+      <c r="A18" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B18" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="1" t="str">
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>27.520360690410925</v>
+      </c>
+      <c r="F18" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="str">
+        <v>1372.4796393095892</v>
+      </c>
+      <c r="G18" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="2"/>
+        <v>19999.999999999087</v>
       </c>
     </row>
   </sheetData>
